--- a/Pruebas calificadas/COLEGIO-CIUDAD-CHENGDU-(IED)-701_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-CIUDAD-CHENGDU-(IED)-701_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -1578,7 +1562,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDÚ (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -1831,7 +1811,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -2337,7 +2309,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -2590,7 +2558,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -2843,7 +2807,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3084,11 +3048,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -3096,7 +3056,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3337,11 +3297,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -3349,7 +3305,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3586,11 +3542,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -3598,7 +3550,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3839,11 +3791,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -3851,7 +3799,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4088,11 +4036,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -4100,7 +4044,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4341,11 +4285,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -4353,7 +4293,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4594,11 +4534,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -4606,7 +4542,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4767,11 +4703,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -4779,7 +4711,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5020,11 +4952,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -5032,7 +4960,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5269,11 +5197,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -5281,7 +5205,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5522,11 +5446,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -5534,7 +5454,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5775,11 +5695,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -5787,7 +5703,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6028,11 +5944,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -6040,7 +5952,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6273,11 +6185,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -6285,7 +6193,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6526,11 +6434,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -6538,7 +6442,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6779,11 +6683,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -6791,7 +6691,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7032,11 +6932,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -7044,7 +6940,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7285,11 +7181,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -7297,7 +7189,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7538,11 +7430,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -7550,7 +7438,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7791,11 +7679,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -7803,7 +7687,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8044,11 +7928,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -8056,7 +7936,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8297,11 +8177,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -8309,7 +8185,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8550,11 +8426,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -8562,7 +8434,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8803,11 +8675,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -8815,7 +8683,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9056,11 +8924,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -9068,7 +8932,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9309,11 +9173,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -9321,7 +9181,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9562,11 +9422,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -9574,7 +9430,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9815,11 +9671,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -9827,7 +9679,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10068,11 +9920,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -10080,7 +9928,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10321,11 +10169,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -10333,7 +10177,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10574,11 +10418,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -10586,7 +10426,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -10827,11 +10667,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -10839,7 +10675,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -11080,11 +10916,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -11092,7 +10924,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -11333,11 +11165,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -11345,7 +11173,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -11586,11 +11414,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -11598,7 +11422,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -11839,11 +11663,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -11851,7 +11671,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -12092,11 +11912,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -12104,7 +11920,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -12345,11 +12161,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -12357,7 +12169,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -12598,11 +12410,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -12610,7 +12418,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -12851,11 +12659,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -12863,7 +12667,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -13104,11 +12908,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -13116,7 +12916,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -13357,11 +13157,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -13369,7 +13165,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -13610,11 +13406,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -13622,7 +13414,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -13863,11 +13655,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -13875,7 +13663,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -14116,11 +13904,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -14128,7 +13912,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -14369,11 +14153,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -14381,7 +14161,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -14622,11 +14402,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -14634,7 +14410,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -14871,11 +14647,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -14883,7 +14655,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -15124,11 +14896,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -15136,7 +14904,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -15377,11 +15145,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -15389,7 +15153,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -15630,11 +15394,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -15642,7 +15402,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -15883,11 +15643,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -15895,7 +15651,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -16136,11 +15892,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -16148,7 +15900,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -16389,11 +16141,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -16401,7 +16149,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -16638,11 +16386,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -16650,7 +16394,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -16891,11 +16635,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -16903,7 +16643,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -17144,11 +16884,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -17156,7 +16892,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -17397,11 +17133,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -17409,7 +17141,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -17650,11 +17382,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -17662,7 +17390,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -17903,11 +17631,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -17915,7 +17639,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -18156,11 +17880,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -18168,7 +17888,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -18409,11 +18129,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -18421,7 +18137,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -18662,11 +18378,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -18674,7 +18386,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -18915,11 +18627,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -18927,7 +18635,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -19168,11 +18876,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -19180,7 +18884,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -19421,11 +19125,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -19433,7 +19133,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -19674,11 +19374,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -19686,7 +19382,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -19927,11 +19623,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -19939,7 +19631,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -20180,11 +19872,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -20192,7 +19880,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -20429,11 +20117,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -20441,7 +20125,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -20682,11 +20366,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="inlineStr"/>
       <c r="B81" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -20694,7 +20374,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -20935,11 +20615,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A82" s="2" t="inlineStr"/>
       <c r="B82" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -20947,7 +20623,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -21188,11 +20864,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A83" s="2" t="inlineStr"/>
       <c r="B83" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -21200,7 +20872,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -21441,11 +21113,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A84" s="2" t="inlineStr"/>
       <c r="B84" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -21453,7 +21121,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -21694,11 +21362,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A85" s="2" t="inlineStr"/>
       <c r="B85" s="2" t="inlineStr">
         <is>
           <t>111001800660</t>
@@ -21706,7 +21370,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO CIUDAD CHENGDU (IED)</t>
+          <t>COLEGIO CIUDAD CHENGDU (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
